--- a/artfynd/A 13482-2022 artfynd.xlsx
+++ b/artfynd/A 13482-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 13482-2022 artfynd.xlsx
+++ b/artfynd/A 13482-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>102897609</v>
+        <v>104025323</v>
       </c>
       <c r="B2" t="n">
         <v>77259</v>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>564523.9096292335</v>
+        <v>564523.8915844829</v>
       </c>
       <c r="R2" t="n">
-        <v>7014548.055136485</v>
+        <v>7014548.955891911</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-08-15</t>
+          <t>2022-08-14</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-08-15</t>
+          <t>2022-08-14</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,19 +775,23 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>102897607</v>
+        <v>104025313</v>
       </c>
       <c r="B3" t="n">
         <v>77506</v>
@@ -827,13 +831,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>564476.4384072943</v>
+        <v>564477.3403845849</v>
       </c>
       <c r="R3" t="n">
-        <v>7014575.489551466</v>
+        <v>7014575.507607721</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,22 +861,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-08-15</t>
+          <t>2022-08-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-08-15</t>
+          <t>2022-08-14</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,21 +890,25 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1370,7 +1378,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>102897608</v>
+        <v>104025280</v>
       </c>
       <c r="B8" t="n">
         <v>77177</v>
@@ -1410,13 +1418,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564473.1915543203</v>
+        <v>564474.0935240535</v>
       </c>
       <c r="R8" t="n">
-        <v>7014602.457706436</v>
+        <v>7014602.475761819</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1440,22 +1448,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-08-15</t>
+          <t>2022-08-14</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-08-15</t>
+          <t>2022-08-14</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1470,22 +1478,26 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>104025313</v>
+        <v>104025283</v>
       </c>
       <c r="B9" t="n">
-        <v>77506</v>
+        <v>78098</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1498,21 +1510,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1522,10 +1534,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>564477.3403845849</v>
+        <v>564495.8671697768</v>
       </c>
       <c r="R9" t="n">
-        <v>7014575.507607721</v>
+        <v>7014641.658825127</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1557,7 +1569,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1567,7 +1579,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1578,11 +1590,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Tall</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1603,10 +1610,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>104025280</v>
+        <v>104025325</v>
       </c>
       <c r="B10" t="n">
-        <v>77177</v>
+        <v>77506</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1619,21 +1626,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1643,10 +1650,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>564474.0935240535</v>
+        <v>564535.2560007214</v>
       </c>
       <c r="R10" t="n">
-        <v>7014602.475761819</v>
+        <v>7014612.261139613</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1678,7 +1685,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1688,7 +1695,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1699,6 +1706,11 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1712,359 +1724,6 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>104025323</v>
-      </c>
-      <c r="B11" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Storberget, Jmt</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>564523.8915844829</v>
-      </c>
-      <c r="R11" t="n">
-        <v>7014548.955891911</v>
-      </c>
-      <c r="S11" t="n">
-        <v>10</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AD11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>104025283</v>
-      </c>
-      <c r="B12" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>6453</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Vedskivlav</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Hertelidea botryosa</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Storberget, Jmt</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>564495.8671697768</v>
-      </c>
-      <c r="R12" t="n">
-        <v>7014641.658825127</v>
-      </c>
-      <c r="S12" t="n">
-        <v>10</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>11:34</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>11:34</t>
-        </is>
-      </c>
-      <c r="AD12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>104025325</v>
-      </c>
-      <c r="B13" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Storberget, Jmt</t>
-        </is>
-      </c>
-      <c r="Q13" t="n">
-        <v>564535.2560007214</v>
-      </c>
-      <c r="R13" t="n">
-        <v>7014612.261139613</v>
-      </c>
-      <c r="S13" t="n">
-        <v>10</v>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="AD13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Tall</t>
-        </is>
-      </c>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
